--- a/data/gravel/Tritao Aveio 2025.xlsx
+++ b/data/gravel/Tritao Aveio 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE13F0A6-5E0E-0D41-AC2D-BE41CA0CE7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E441CBB1-7266-AD43-AC31-91F4F108425C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26500" yWindow="-19260" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>a8:i34</t>
+  </si>
+  <si>
+    <t>https://cdn.prod.website-files.com/66b74a02e94ee47108014577/66b77ff281ce1bdd25b0af90_Tritao_titan_aveiro_3d-printed_gravel_bike.jpg</t>
   </si>
 </sst>
 </file>
@@ -776,6 +779,11 @@
         <v>105</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Tritao Aveio 2025.xlsx
+++ b/data/gravel/Tritao Aveio 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E441CBB1-7266-AD43-AC31-91F4F108425C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D283602-9AFD-8540-8C9F-0EB18F1B8971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -353,9 +353,6 @@
     <t>https://www.tritaobikes.com/aveiro</t>
   </si>
   <si>
-    <t>euro</t>
-  </si>
-  <si>
     <t>*not spec'd</t>
   </si>
   <si>
@@ -366,6 +363,15 @@
   </si>
   <si>
     <t>https://cdn.prod.website-files.com/66b74a02e94ee47108014577/66b77ff281ce1bdd25b0af90_Tritao_titan_aveiro_3d-printed_gravel_bike.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Troviscal, Aveiro, Portugal</t>
+  </si>
+  <si>
+    <t>EUR</t>
   </si>
 </sst>
 </file>
@@ -731,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -781,7 +787,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -789,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -818,7 +824,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1358,7 +1364,7 @@
         <v>50</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -1784,7 +1790,15 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Tritao Aveio 2025.xlsx
+++ b/data/gravel/Tritao Aveio 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D283602-9AFD-8540-8C9F-0EB18F1B8971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5113FF-3E25-424A-B470-B885246FEF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -737,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1625,161 +1643,143 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="1">
-        <v>30.9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="1">
-        <v>160</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="1">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="1">
+        <v>30.9</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B63" s="1">
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B64" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B71" s="1">
-        <v>3350</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="1">
-        <v>5550</v>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>67</v>
@@ -1787,17 +1787,65 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="1">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>111</v>
       </c>
     </row>
